--- a/расчет батча.xlsx
+++ b/расчет батча.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Grid Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D297C3E-335F-43E4-A731-A1E00F559E31}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B990A3-3C5D-454C-A095-76A0A8553F92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F4793AFB-05E6-43C9-9995-743683279B2A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>белые</t>
   </si>
@@ -39,18 +39,9 @@
     <t>черные</t>
   </si>
   <si>
-    <t>линии</t>
-  </si>
-  <si>
     <t>всего вариаций</t>
   </si>
   <si>
-    <t>ширина</t>
-  </si>
-  <si>
-    <t>высота</t>
-  </si>
-  <si>
     <t>степень</t>
   </si>
   <si>
@@ -60,13 +51,13 @@
     <t>макс - 15</t>
   </si>
   <si>
-    <t>макс - 20</t>
-  </si>
-  <si>
     <t>кол-во батчей</t>
   </si>
   <si>
     <t>время</t>
+  </si>
+  <si>
+    <t>огр. по инту</t>
   </si>
 </sst>
 </file>
@@ -435,53 +426,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DAEF886-1896-4531-A892-2B8D974133E5}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="48.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="55.7109375" customWidth="1"/>
-    <col min="9" max="9" width="60.140625" customWidth="1"/>
-    <col min="10" max="10" width="40.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="6" max="6" width="37" customWidth="1"/>
+    <col min="7" max="7" width="40.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>12^B2</f>
         <v>1.5407021574586368E+16</v>
@@ -497,116 +477,78 @@
         <v>8</v>
       </c>
       <c r="E2" s="1">
-        <f>7^(F2*G2-3*(B2+D2))</f>
-        <v>1.5777538203484581E+26</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
+        <f>A2*C2</f>
+        <v>1.0097145659120922E+21</v>
+      </c>
+      <c r="F2" s="1">
+        <f>E2/E3</f>
+        <v>322486272</v>
       </c>
       <c r="G2" s="1">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1">
-        <f>A2*C2*E2</f>
-        <v>1.5930810138292884E+47</v>
-      </c>
-      <c r="I2" s="1">
-        <f>H2/H3</f>
-        <v>5.4159494736724613E+25</v>
-      </c>
-      <c r="J2" s="1">
-        <f>I2*J3/60/60</f>
-        <v>4.5132912280603838E+24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <f>F2*G3/60/60</f>
+        <v>1791.5904000000003</v>
+      </c>
+      <c r="H2">
+        <f>G2/100</f>
+        <v>17.915904000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>12^B3</f>
-        <v>144</v>
+        <v>2985984</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
         <f>4^D3</f>
-        <v>256</v>
+        <v>1048576</v>
       </c>
       <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1">
+        <f>A3*C3</f>
+        <v>3131031158784</v>
+      </c>
+      <c r="F3" s="1" t="b">
+        <f>F2&lt;=A8</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="b">
+        <f>A3&lt;=A8</f>
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1">
-        <f>7^F3</f>
-        <v>7.9792266297612E+16</v>
-      </c>
-      <c r="F3">
-        <v>20</v>
-      </c>
-      <c r="H3" s="1">
-        <f>A3*C3*E3</f>
-        <v>2.9414621047951689E+21</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="C4" s="1" t="b">
+        <f>C3&lt;=A8</f>
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <f>2^31-1</f>
         <v>2147483647</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1">
-        <f>2^31-1</f>
-        <v>2147483647</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1">
-        <f>2^63-1</f>
-        <v>9.2233720368547758E+18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="1" t="b">
-        <f>I2&lt;=A4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="b">
-        <f>A3&lt;=A4</f>
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="b">
-        <f t="shared" ref="C5" si="0">C3&lt;=C4</f>
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="b">
-        <f>E3&lt;=E4</f>
-        <v>1</v>
-      </c>
-      <c r="H5" t="b">
-        <f>H3&lt;=E4</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="b">
-        <f>I2&lt;=E4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <f>A3*C3</f>
-        <v>36864</v>
-      </c>
-      <c r="E6" s="1" t="b">
-        <f>E2&lt;=E4</f>
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/расчет батча.xlsx
+++ b/расчет батча.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Grid Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B990A3-3C5D-454C-A095-76A0A8553F92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B257F9EF-4CDC-42D1-8B8E-0DCCC0E0D425}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F4793AFB-05E6-43C9-9995-743683279B2A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>белые</t>
   </si>
@@ -58,12 +58,24 @@
   </si>
   <si>
     <t>огр. по инту</t>
+  </si>
+  <si>
+    <t>огр. по лонгу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">макс - </t>
+  </si>
+  <si>
+    <t>&gt; 30 мин</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -103,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -112,6 +124,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -430,126 +446,167 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="14" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="40.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <f>12^B2</f>
+      <c r="B2" s="1">
+        <f>12^C2</f>
         <v>1.5407021574586368E+16</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>15</v>
       </c>
-      <c r="C2" s="1">
-        <f>4^D2</f>
+      <c r="D2" s="1">
+        <f>4^E2</f>
         <v>65536</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>8</v>
       </c>
-      <c r="E2" s="1">
-        <f>A2*C2</f>
+      <c r="F2" s="1">
+        <f>B2*D2</f>
         <v>1.0097145659120922E+21</v>
       </c>
-      <c r="F2" s="1">
-        <f>E2/E3</f>
-        <v>322486272</v>
-      </c>
       <c r="G2" s="1">
-        <f>F2*G3/60/60</f>
-        <v>1791.5904000000003</v>
-      </c>
-      <c r="H2">
-        <f>G2/100</f>
-        <v>17.915904000000001</v>
+        <f>F2/F3</f>
+        <v>8916100448256</v>
+      </c>
+      <c r="H2" s="5">
+        <f>G2*H3/60/60</f>
+        <v>619173642240</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <f>12^B3</f>
-        <v>2985984</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1">
-        <f>4^D3</f>
-        <v>1048576</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1">
-        <f>A3*C3</f>
-        <v>3131031158784</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <f>F2&lt;=A8</f>
+      <c r="B3" s="1">
+        <f>12^C3</f>
+        <v>1728</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1">
+        <f>4^E3</f>
+        <v>65536</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1">
+        <f>B3*D3</f>
+        <v>113246208</v>
+      </c>
+      <c r="H3" s="5">
+        <f>250</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="b">
+        <f>B3&lt;=A5</f>
         <v>1</v>
       </c>
-      <c r="G3" s="1">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="b">
-        <f>A3&lt;=A8</f>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <f>D3&lt;=A5</f>
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="b">
-        <f>C3&lt;=A8</f>
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="b">
+        <f>G2&lt;=A5</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F5" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="A5" s="1">
         <f>2^31-1</f>
         <v>2147483647</v>
       </c>
+      <c r="B5" s="1"/>
+      <c r="C5"/>
+      <c r="D5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="b">
+        <f>B3&lt;=A7</f>
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <f>D3&lt;=A7</f>
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="b">
+        <f>G2&lt;=A7</f>
+        <v>1</v>
+      </c>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f>2^63-1</f>
+        <v>9.2233720368547758E+18</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7" s="1"/>
+      <c r="G7"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8"/>
+      <c r="D8" s="1"/>
+      <c r="G8"/>
+      <c r="H8" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/расчет батча.xlsx
+++ b/расчет батча.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Grid Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B257F9EF-4CDC-42D1-8B8E-0DCCC0E0D425}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5D31CD-131D-4DA6-9E52-0FB1DF7B3622}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F4793AFB-05E6-43C9-9995-743683279B2A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
   <si>
     <t>белые</t>
   </si>
@@ -442,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DAEF886-1896-4531-A892-2B8D974133E5}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
@@ -608,6 +608,152 @@
       <c r="G8"/>
       <c r="H8" s="5"/>
     </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="1">
+        <f>12^C10</f>
+        <v>248832</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1">
+        <f>4^E10</f>
+        <v>4096</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1">
+        <f>B10*D10</f>
+        <v>1019215872</v>
+      </c>
+      <c r="G10" s="1">
+        <f>F10/F11</f>
+        <v>9</v>
+      </c>
+      <c r="H10" s="5">
+        <f>G10*H11/60/60</f>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="1">
+        <f>12^C11</f>
+        <v>1728</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <f>4^E11</f>
+        <v>65536</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1">
+        <f>B11*D11</f>
+        <v>113246208</v>
+      </c>
+      <c r="H11" s="5">
+        <f>250</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="b">
+        <f>B11&lt;=A13</f>
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="b">
+        <f>D11&lt;=A13</f>
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="1" t="b">
+        <f>G10&lt;=A13</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <f>2^31-1</f>
+        <v>2147483647</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13"/>
+      <c r="D13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="b">
+        <f>B11&lt;=A15</f>
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="b">
+        <f>D11&lt;=A15</f>
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" t="b">
+        <f>G10&lt;=A15</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f>2^63-1</f>
+        <v>9.2233720368547758E+18</v>
+      </c>
+      <c r="C15"/>
+      <c r="D15" s="1"/>
+      <c r="G15"/>
+      <c r="H15" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/расчет батча.xlsx
+++ b/расчет батча.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Grid Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5D31CD-131D-4DA6-9E52-0FB1DF7B3622}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD90A5EF-1BEB-42A3-89FE-9AA5C7D56A62}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F4793AFB-05E6-43C9-9995-743683279B2A}"/>
   </bookViews>
@@ -499,7 +499,7 @@
         <v>1.0097145659120922E+21</v>
       </c>
       <c r="G2" s="1">
-        <f>F2/F3</f>
+        <f>_xlfn.CEILING.MATH(B2/B3)*_xlfn.CEILING.MATH(D2/D3)</f>
         <v>8916100448256</v>
       </c>
       <c r="H2" s="5">
@@ -634,10 +634,10 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <f>12^C10</f>
-        <v>248832</v>
+        <v>20736</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="1">
         <f>4^E10</f>
@@ -648,15 +648,15 @@
       </c>
       <c r="F10" s="1">
         <f>B10*D10</f>
-        <v>1019215872</v>
+        <v>84934656</v>
       </c>
       <c r="G10" s="1">
-        <f>F10/F11</f>
-        <v>9</v>
+        <f>_xlfn.CEILING.MATH(B10/B11)*_xlfn.CEILING.MATH(D10/D11)</f>
+        <v>12</v>
       </c>
       <c r="H10" s="5">
         <f>G10*H11/60/60</f>
-        <v>0.625</v>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -679,8 +679,8 @@
         <v>113246208</v>
       </c>
       <c r="H11" s="5">
-        <f>250</f>
-        <v>250</v>
+        <f>20</f>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">

--- a/расчет батча.xlsx
+++ b/расчет батча.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Grid Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD90A5EF-1BEB-42A3-89FE-9AA5C7D56A62}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056F25F8-F3AD-48B0-8F83-F69D3EF262F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F4793AFB-05E6-43C9-9995-743683279B2A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
   <si>
     <t>белые</t>
   </si>
@@ -66,7 +66,10 @@
     <t xml:space="preserve">макс - </t>
   </si>
   <si>
-    <t>&gt; 30 мин</t>
+    <t>1 батч - 20 сек</t>
+  </si>
+  <si>
+    <t>1 батч - 20 мин</t>
   </si>
 </sst>
 </file>
@@ -446,7 +449,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.42578125" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -481,8 +484,8 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1">
-        <f>12^C2</f>
-        <v>1.5407021574586368E+16</v>
+        <f>16^C2</f>
+        <v>1.152921504606847E+18</v>
       </c>
       <c r="C2">
         <v>15</v>
@@ -496,21 +499,21 @@
       </c>
       <c r="F2" s="1">
         <f>B2*D2</f>
-        <v>1.0097145659120922E+21</v>
+        <v>7.5557863725914323E+22</v>
       </c>
       <c r="G2" s="1">
         <f>_xlfn.CEILING.MATH(B2/B3)*_xlfn.CEILING.MATH(D2/D3)</f>
-        <v>8916100448256</v>
+        <v>281474976710656</v>
       </c>
       <c r="H2" s="5">
         <f>G2*H3/60/60</f>
-        <v>619173642240</v>
+        <v>140737488355328</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
-        <f>12^C3</f>
-        <v>1728</v>
+        <f>16^C3</f>
+        <v>4096</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -524,11 +527,11 @@
       </c>
       <c r="F3" s="1">
         <f>B3*D3</f>
-        <v>113246208</v>
+        <v>268435456</v>
       </c>
       <c r="H3" s="5">
-        <f>250</f>
-        <v>250</v>
+        <f>60*30</f>
+        <v>1800</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -554,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -633,8 +636,8 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
-        <f>12^C10</f>
-        <v>20736</v>
+        <f>16^C10</f>
+        <v>65536</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -648,21 +651,21 @@
       </c>
       <c r="F10" s="1">
         <f>B10*D10</f>
-        <v>84934656</v>
+        <v>268435456</v>
       </c>
       <c r="G10" s="1">
         <f>_xlfn.CEILING.MATH(B10/B11)*_xlfn.CEILING.MATH(D10/D11)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H10" s="5">
         <f>G10*H11/60/60</f>
-        <v>6.6666666666666666E-2</v>
+        <v>8.8888888888888878E-2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
-        <f>12^C11</f>
-        <v>1728</v>
+        <f>16^C11</f>
+        <v>4096</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -676,7 +679,7 @@
       </c>
       <c r="F11" s="1">
         <f>B11*D11</f>
-        <v>113246208</v>
+        <v>268435456</v>
       </c>
       <c r="H11" s="5">
         <f>20</f>

--- a/расчет батча.xlsx
+++ b/расчет батча.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Grid Calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056F25F8-F3AD-48B0-8F83-F69D3EF262F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AD9860-6A17-4774-96A5-AF41B8B14FFC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F4793AFB-05E6-43C9-9995-743683279B2A}"/>
   </bookViews>
@@ -600,6 +600,10 @@
         <f>2^63-1</f>
         <v>9.2233720368547758E+18</v>
       </c>
+      <c r="B7" t="b">
+        <f>B2&lt;=A7</f>
+        <v>1</v>
+      </c>
       <c r="C7"/>
       <c r="D7" s="1"/>
       <c r="G7"/>
